--- a/outputs/may-2026-real-events/details/02-kintex-playx4-2026/bundle/tables/safety-checklists.xlsx
+++ b/outputs/may-2026-real-events/details/02-kintex-playx4-2026/bundle/tables/safety-checklists.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/Volumes/data/Dev/korea-mice-safety-agent/outputs/may-2026-real-events/details/02-kintex-playx4-2026</t>
+          <t>outputs/may-2026-real-events/details/02-kintex-playx4-2026</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>개장 T-75</t>
+          <t>개장 T-60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2572,27 +2572,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>출입통제·VIP·보안검색</t>
+          <t>등록·CCTV·촬영</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>보안검색 위치, 검색 예외, VIP 동선, 경비원 명부, 경찰·베뉴 보안실 연락 기준 확인</t>
+          <t>개인정보 고지, CCTV 안내판, 촬영 고지, 현장 단말 잠금, 접근권한, 접속기록 담당 확인</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>보안팀장</t>
+          <t>개인정보보호책임자</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>보안 배치표/명부/무전망</t>
+          <t>고지문/안내판 사진/권한 점검표</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>경찰/안전총괄</t>
+          <t>운영총괄/보안책임자</t>
         </is>
       </c>
     </row>
@@ -2614,27 +2614,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>등록·CCTV·촬영</t>
+          <t>객석·스탠딩 구역</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>개인정보 고지, CCTV 안내판, 촬영 고지, 현장 단말 잠금, 접근권한, 접속기록 담당 확인</t>
+          <t>스탠딩 펜스, 무대 전면 압박 완충, 피난통로, 보안·의료 전진배치, 피난안내 방송문 확인</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>개인정보보호책임자</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>고지문/안내판 사진/권한 점검표</t>
+          <t>객석 도면/펜스 사진/무전 체크</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>운영총괄/보안책임자</t>
+          <t>보안팀/의료팀/안전총괄</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>개장 T-60</t>
+          <t>개장 T-45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2656,39 +2656,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>객석·스탠딩 구역</t>
+          <t>전체 스태프</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>스탠딩 펜스, 무대 전면 압박 완충, 피난통로, 보안·의료 전진배치, 피난안내 방송문 확인</t>
+          <t>안전 브리핑, 구역별 보고선, 무전 채널, 대피/중지/재개 방송문, 미아·분실·민원 처리 기준 공유</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>공연안전 담당</t>
+          <t>안전총괄</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>객석 도면/펜스 사진/무전 체크</t>
+          <t>브리핑 참석명단/무전 체크</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>보안팀/의료팀/안전총괄</t>
+          <t>운영총괄</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>개장 전</t>
+          <t>공연 직전</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>개장 T-45</t>
+          <t>공연 T-15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2698,39 +2698,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>전체 스태프</t>
+          <t>무대감독·운영본부</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>안전 브리핑, 구역별 보고선, 무전 채널, 대피/중지/재개 방송문, 미아·분실·민원 처리 기준 공유</t>
+          <t>공연중지 기준, 아티스트/무대감독 중지 신호, 전원 차단, 비상방송, 관객 현 위치 대기·분산 문구 공유</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>무대감독</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>브리핑 참석명단/무전 체크</t>
+          <t>무대감독 체크/방송문 승인/무전 로그</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>운영총괄</t>
+          <t>운영총괄/안전총괄</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>공연 직전</t>
+          <t>개장 전</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공연 T-15</t>
+          <t>개장 T-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2740,39 +2740,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>무대감독·운영본부</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>공연중지 기준, 아티스트/무대감독 중지 신호, 전원 차단, 비상방송, 관객 현 위치 대기·분산 문구 공유</t>
+          <t>개장 승인 hold point: 소방·피난, 의료, 보안, 동선, 전기, 식음료, 작업구역 이상 없음 확인 후 개장</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>무대감독</t>
+          <t>운영총괄</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>무대감독 체크/방송문 승인/무전 로그</t>
+          <t>개장 승인 체크/무전 로그</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>운영총괄/안전총괄</t>
+          <t>안전총괄</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>개장 전</t>
+          <t>운영 중</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>개장 T-15</t>
+          <t>30분 간격</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2782,39 +2782,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>운영본부</t>
+          <t>게이트·혼잡 구역</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>개장 승인 hold point: 소방·피난, 의료, 보안, 동선, 전기, 식음료, 작업구역 이상 없음 확인 후 개장</t>
+          <t>구역별 체류 인원, 대기열 길이, 병목, 우회동선, 스태프 피로도, 위험 신고를 주기 보고</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>운영총괄</t>
+          <t>구역장</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>개장 승인 체크/무전 로그</t>
+          <t>순찰 로그/사진</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>안전총괄/보안팀</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>운영 중</t>
+          <t>공연 중</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30분 간격</t>
+          <t>15분 간격</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2824,39 +2824,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>게이트·혼잡 구역</t>
+          <t>무대 전면·스탠딩 구역</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>구역별 체류 인원, 대기열 길이, 병목, 우회동선, 스태프 피로도, 위험 신고를 주기 보고</t>
+          <t>무대 전면 압박, 펜스 변형, 관객 쓰러짐, 역류, 응급환자, 구조물 흔들림, 전기 이상 징후 보고</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>구역장</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>순찰 로그/사진</t>
+          <t>순찰 로그/현장 사진/의료·보안 출동 기록</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>안전총괄/보안팀</t>
+          <t>무대감독/안전총괄/의료·보안</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>공연 중</t>
+          <t>피크</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15분 간격</t>
+          <t>피크 T-30~T+30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2866,39 +2866,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>무대 전면·스탠딩 구역</t>
+          <t>주요 입퇴장 동선</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>무대 전면 압박, 펜스 변형, 관객 쓰러짐, 역류, 응급환자, 구조물 흔들림, 전기 이상 징후 보고</t>
+          <t>혼잡 단계 상향 기준, 입장 속도 조절, 우회 안내, 의료·보안 전진 배치, 방송문 준비</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>공연안전 담당</t>
+          <t>안전총괄</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>순찰 로그/현장 사진/의료·보안 출동 기록</t>
+          <t>피크 점검 로그/방송 승인</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>무대감독/안전총괄/의료·보안</t>
+          <t>운영총괄/경찰·소방</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>피크</t>
+          <t>폐장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피크 T-30~T+30</t>
+          <t>폐장 T-30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2908,39 +2908,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>주요 입퇴장 동선</t>
+          <t>퇴장 동선</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>혼잡 단계 상향 기준, 입장 속도 조절, 우회 안내, 의료·보안 전진 배치, 방송문 준비</t>
+          <t>퇴장 분산 방송, 역/주차장/셔틀 대기열, 야간 조명, 우회동선, 미아·응급 잔여 이슈 확인</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>구역장</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>폐장 전 점검표/방송 로그</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>피크 점검 로그/방송 승인</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>운영총괄/경찰·소방</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>폐장</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>폐장 T-30</t>
+          <t>공연 종료 후</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2950,39 +2950,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>퇴장 동선</t>
+          <t>퇴장·무대 구역</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>퇴장 분산 방송, 역/주차장/셔틀 대기열, 야간 조명, 우회동선, 미아·응급 잔여 이슈 확인</t>
+          <t>퇴장 분산, 무대 접근통제, 전원 차단, 특수효과·화기 종료, 철거 전 관객 완전 분리 확인</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>구역장</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>폐장 전 점검표/방송 로그</t>
+          <t>퇴장 로그/전원 차단 확인/철거 전 사진</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>무대감독/안전총괄</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>폐장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공연 종료 후</t>
+          <t>폐장 후 T+30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2992,39 +2992,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>퇴장·무대 구역</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>퇴장 분산, 무대 접근통제, 전원 차단, 특수효과·화기 종료, 철거 전 관객 완전 분리 확인</t>
+          <t>사고·응급·민원·분실·미아 기록 취합, 미해결 조치 담당자 지정, 관계기관 종료 공유</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>공연안전 담당</t>
+          <t>운영본부 기록담당</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>퇴장 로그/전원 차단 확인/철거 전 사진</t>
+          <t>일일 운영 종료 보고</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>무대감독/안전총괄</t>
+          <t>운영총괄</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>폐장</t>
+          <t>철거</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>폐장 후 T+30</t>
+          <t>철거 전</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3034,27 +3034,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>운영본부</t>
+          <t>작업구역</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>사고·응급·민원·분실·미아 기록 취합, 미해결 조치 담당자 지정, 관계기관 종료 공유</t>
+          <t>관람객 완전 분리, 전기 차단/투입 승인, 작업허가, PPE, 추락·중량물·화기 작업 통제선 확인</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>운영본부 기록담당</t>
+          <t>작업책임자</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>일일 운영 종료 보고</t>
+          <t>작업허가/교육명단/사진</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>운영총괄</t>
+          <t>안전총괄/베뉴 담당</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>철거 전</t>
+          <t>철거 중</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3076,109 +3076,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>작업구역</t>
+          <t>하역·반출 동선</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>관람객 완전 분리, 전기 차단/투입 승인, 작업허가, PPE, 추락·중량물·화기 작업 통제선 확인</t>
+          <t>지게차·하역장·차량 동선과 보행동선 분리, 하중분산, 잔재물 낙하·전도 위험 확인</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>작업책임자</t>
+          <t>하역책임자</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>작업허가/교육명단/사진</t>
+          <t>하역 순찰 로그/사진</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>안전총괄/베뉴 담당</t>
+          <t>시설담당/안전총괄</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>철거</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>철거 중</t>
+          <t>D+1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>하역·반출 동선</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>지게차·하역장·차량 동선과 보행동선 분리, 하중분산, 잔재물 낙하·전도 위험 확인</t>
+          <t>사고보고서, 조치 전후 사진, 제출·승인 증빙, 개인정보 파기/보존, 베뉴 원상복구 확인 정리</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>하역책임자</t>
+          <t>운영본부 기록담당</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>하역 순찰 로그/사진</t>
+          <t>종료 보고서/증빙철</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
-        <is>
-          <t>시설담당/안전총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>종료</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D+1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>운영본부</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>사고보고서, 조치 전후 사진, 제출·승인 증빙, 개인정보 파기/보존, 베뉴 원상복구 확인 정리</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>운영본부 기록담당</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>종료 보고서/증빙철</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
         <is>
           <t>운영총괄</t>
         </is>
@@ -3190,7 +3148,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3275,27 +3233,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>경기도 고양시 안전/행사 담당부서</t>
+          <t>관할 건축부서/베뉴 시설팀</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>옥외행사·지역축제 안전관리계획서</t>
+          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>옥외축제, 야외 공연, 주최/주관 행사 또는 순간 최대 인파 기준 해당 시</t>
+          <t>대형 텐트, 임시 전시장, 복층/다층 임시구조물, 공사 중 구역 임시 사용</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>표시·설치 전 허가/신고 및 게시대 신청 기한을 관할 지자체 기준으로 확인</t>
+          <t>설치 전 신고·승인, 개장 전 피난안전 확인</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>지자체 조례 우선순위 후보와 재난안전법 지역축제/다중운집 조항 확인</t>
+          <t>건축법 시행규칙 별지 제8·8의2·17호서식</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3312,27 +3270,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>옥외광고 담당부서/베뉴</t>
+          <t>베뉴 운영/시설/전기/방재 담당</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
+          <t>부스 시공, 전기, 하역, 소방통로, 반입제한, 제출 안전서류</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>옥외 임시 안내물, 지주형 표시물, 전광류 또는 전기 사용 광고물을 설치하는 경우</t>
+          <t>전시장·컨벤션센터·공연장 등 베뉴를 사용하는 경우</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>표시·설치 전</t>
+          <t>주최자 매뉴얼 기한, 시공 전, 개장 전</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>옥외광고물법 시행령 제5·7·12·14조와 관할 조례 확인</t>
+          <t>킨텍스 운영규정/안전수칙과 venue-facility sourceSpan 확인</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3349,27 +3307,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관할 건축부서/베뉴 시설팀</t>
+          <t>소방서/베뉴 방재실/안전총괄</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
+          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대형 텐트, 임시 전시장, 복층/다층 임시구조물, 공사 중 구역 임시 사용</t>
+          <t>화기, 위험물, 임시전기, 부스·무대 설치, 피난통로 차단 위험이 있는 경우</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>설치 전 신고·승인, 개장 전 피난안전 확인</t>
+          <t>설치 전, 개장 전, 피크 전, 철거 전</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>건축법 시행규칙 별지 제8·8의2·17호서식</t>
+          <t>화재예방법·소방시설법 하위 별표와 베뉴 방재실 승인조건</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3386,27 +3344,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>베뉴 운영/시설/전기/방재 담당</t>
+          <t>개인정보 보호책임자/등록 대행사/보안 담당</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>부스 시공, 전기, 하역, 소방통로, 반입제한, 제출 안전서류</t>
+          <t>개인정보 처리방침, 위탁계약, CCTV 안내, 접근권한·접속기록 점검</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>전시장·컨벤션센터·공연장 등 베뉴를 사용하는 경우</t>
+          <t>등록, QR/출입증, CCTV, 촬영, 앱 신고, VIP/초청자 명단 처리</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>주최자 매뉴얼 기한, 시공 전, 개장 전</t>
+          <t>수집 전 고지, 행사 전 위탁·보안점검, 종료 후 파기</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>킨텍스 운영규정/안전수칙과 venue-facility sourceSpan 확인</t>
+          <t>개인정보보호법 제15·22·25·26·29·30조와 시행령 안전성 확보 조치</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3423,27 +3381,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/안전총괄</t>
+          <t>의료담당/AED 관리책임자/119·이송병원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
+          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>화기, 위험물, 임시전기, 부스·무대 설치, 피난통로 차단 위험이 있는 경우</t>
+          <t>대규모 인파, 고령자/영유아/장애인, 스탠딩 공연, 야외·폭염·야간 행사</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>설치 전, 개장 전, 피크 전, 철거 전</t>
+          <t>개장 전, 운영 중, 사용/이송 발생 시</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>화재예방법·소방시설법 하위 별표와 베뉴 방재실 승인조건</t>
+          <t>응급의료법 AED 설치·관리, 시행규칙 구급차 장비·운행기록 기준</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3460,141 +3418,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자/등록 대행사/보안 담당</t>
+          <t>시공/하역/전기 협력사/안전총괄</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보 처리방침, 위탁계약, CCTV 안내, 접근권한·접속기록 점검</t>
+          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>등록, QR/출입증, CCTV, 촬영, 앱 신고, VIP/초청자 명단 처리</t>
+          <t>부스·무대·트러스·전기·고소·중량물·화기·철거 작업이 있는 경우</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>수집 전 고지, 행사 전 위탁·보안점검, 종료 후 파기</t>
+          <t>작업 전, 작업 중 변경 시, 철거 전</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>개인정보보호법 제15·22·25·26·29·30조와 시행령 안전성 확보 조치</t>
+          <t>산안법, 산안기준규칙 제38·42·321조, KOSHA Guide worker-safety layer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>경찰/경비업체/베뉴 보안실</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>경비업 허가 범위, 경비지도사, 경비원 명부, 배치·폐지 신고</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VIP, 보안검색, 민간경비, 혼잡·교통유도경비를 운영하는 경우</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>배치 전, 20일 이상 배치 또는 신고 대상 조건 확인</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>경비업법·시행령·시행규칙 별표/별지 서식</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>의료담당/AED 관리책임자/119·이송병원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>대규모 인파, 고령자/영유아/장애인, 스탠딩 공연, 야외·폭염·야간 행사</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>개장 전, 운영 중, 사용/이송 발생 시</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>응급의료법 AED 설치·관리, 시행규칙 구급차 장비·운행기록 기준</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사/안전총괄</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>부스·무대·트러스·전기·고소·중량물·화기·철거 작업이 있는 경우</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>작업 전, 작업 중 변경 시, 철거 전</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>산안법, 산안기준규칙 제38·42·321조, KOSHA Guide worker-safety layer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4983,7 +4830,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -5015,7 +4862,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>376</t>
         </is>
       </c>
     </row>
@@ -5047,7 +4894,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>374</t>
         </is>
       </c>
     </row>
@@ -5079,7 +4926,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -5111,7 +4958,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>493</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5022,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>598</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5054,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>602</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5086,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5118,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5150,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>672</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5182,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>490</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5246,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>709</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5278,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>742</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>228</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5342,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>769</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7839,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8137,17 +7984,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>경기도 고양시 안전/행사 담당부서</t>
+          <t>관할 건축부서/베뉴 시설팀</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>옥외행사·지역축제 안전관리계획서</t>
+          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>local_government</t>
+          <t>local_government | venue | fire_police_medical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8167,27 +8014,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>시설·방재 담당</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>안전총괄</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>운영총괄</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>경기도 고양시 안전/행사 담당부서</t>
+          <t>소방서/베뉴 방재실/시설팀</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>운영본부/협력사</t>
+          <t>운영본부/구역장</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>제출본 PDF/접수증/승인메일/담당자 확인 메모</t>
+          <t>가설건축물 신고필증/피난안전 확인서/임시사용 승인 확인</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -8204,32 +8051,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>옥외광고 담당부서/베뉴</t>
+          <t>베뉴 운영/시설/전기/방재 담당</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
+          <t>부스 시공, 전기, 하역, 소방통로, 반입제한, 제출 안전서류</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>local_government | venue</t>
+          <t>venue | fire_police_medical | worker_contractor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>T-7 설치·작업 전 승인</t>
+          <t>T-1 개장 전 확인</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-20 개장 전 현장 확인</t>
+          <t>2026-05-21 운영 중 재점검</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -8254,7 +8101,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>광고물 허가·신고필증/베뉴 설치 승인/설치 사진</t>
+          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -8271,17 +8118,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관할 건축부서/베뉴 시설팀</t>
+          <t>소방서/베뉴 방재실/안전총괄</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
+          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>local_government | venue | fire_police_medical</t>
+          <t>venue | fire_police_medical | worker_contractor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8321,7 +8168,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>가설건축물 신고필증/피난안전 확인서/임시사용 승인 확인</t>
+          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -8338,57 +8185,57 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>베뉴 운영/시설/전기/방재 담당</t>
+          <t>개인정보 보호책임자/등록 대행사/보안 담당</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>부스 시공, 전기, 하역, 소방통로, 반입제한, 제출 안전서류</t>
+          <t>개인정보 처리방침, 위탁계약, CCTV 안내, 접근권한·접속기록 점검</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>venue | fire_police_medical | worker_contractor</t>
+          <t>local_government | privacy_security</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>T-1 개장 전 확인</t>
+          <t>T-14 사전점검</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-21 운영 중 재점검</t>
+          <t>2026-05-20 고지·권한 최종 확인</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>개인정보보호책임자</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>개인정보보호책임자</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/시설팀</t>
+          <t>등록 대행사/보안 담당</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>운영본부/구역장</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
+          <t>처리방침/위탁계약/안내문/CCTV 고지 사진/접속기록 점검표</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -8405,37 +8252,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/안전총괄</t>
+          <t>의료담당/AED 관리책임자/119·이송병원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
+          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>venue | fire_police_medical | worker_contractor</t>
+          <t>fire_police_medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T-7 설치·작업 전 승인</t>
+          <t>T-1 개장 전 확인</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-20 개장 전 현장 확인</t>
+          <t>2026-05-21 운영 중 재점검</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>의료담당</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8445,7 +8292,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/시설팀</t>
+          <t>119/이송병원/AED 관리책임자</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8455,7 +8302,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
+          <t>AED 점검표/응급인력 배치표/119·이송병원 협의 기록</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -8472,261 +8319,60 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자/등록 대행사/보안 담당</t>
+          <t>시공/하역/전기 협력사/안전총괄</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보 처리방침, 위탁계약, CCTV 안내, 접근권한·접속기록 점검</t>
+          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>local_government | privacy_security</t>
+          <t>venue | worker_contractor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T-14 사전점검</t>
+          <t>T-7 설치·작업 전 승인</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-20 고지·권한 최종 확인</t>
+          <t>2026-05-20 개장 전 현장 확인</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>개인정보보호책임자</t>
+          <t>작업책임자</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>개인정보보호책임자</t>
+          <t>안전총괄</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>등록 대행사/보안 담당</t>
+          <t>시공/하역/전기 협력사</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>운영본부</t>
+          <t>운영본부/구역장</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>처리방침/위탁계약/안내문/CCTV 고지 사진/접속기록 점검표</t>
+          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>경찰/경비업체/베뉴 보안실</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>경비업 허가 범위, 경비지도사, 경비원 명부, 배치·폐지 신고</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>local_government | venue | fire_police_medical | privacy_security</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>T-7 담당기관 확인</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-05-20 최종 확인</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>교통·대외협력 담당</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>도로관리청/경찰/지자체</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>운영본부/안내팀</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>제출본 PDF/접수증/승인메일/담당자 확인 메모</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>의료담당/AED 관리책임자/119·이송병원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>fire_police_medical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>T-1 개장 전 확인</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-05-21 운영 중 재점검</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>의료담당</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>119/이송병원/AED 관리책임자</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>운영본부/구역장</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>AED 점검표/응급인력 배치표/119·이송병원 협의 기록</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사/안전총괄</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>venue | worker_contractor</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>T-7 설치·작업 전 승인</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-05-20 개장 전 현장 확인</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>작업책임자</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>운영본부/구역장</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
         <is>
           <t>open</t>
         </is>

--- a/outputs/may-2026-real-events/details/02-kintex-playx4-2026/bundle/tables/safety-checklists.xlsx
+++ b/outputs/may-2026-real-events/details/02-kintex-playx4-2026/bundle/tables/safety-checklists.xlsx
@@ -7947,7 +7947,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>작업책임자</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7957,17 +7957,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>시공/하역/전기 협력사</t>
+          <t>공연/문화 담당부서·베뉴 기술지원</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>운영본부/구역장</t>
+          <t>운영본부/무대감독/보안·의료팀</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
+          <t>공연 재해대처계획/안전교육 명단/무대·리깅 승인/공연중지 기준</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
+          <t>베뉴 제출 승인서/부스·전기 신청서/반입·하역 승인/현장 확인 사진</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
